--- a/purchase_order_generator/templates/input_template.xlsx
+++ b/purchase_order_generator/templates/input_template.xlsx
@@ -1754,12 +1754,11 @@
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1789,15 +1788,10 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>货号</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1860,7 +1854,7 @@
       <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="L3" t="s">
+      <c r="K3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5188,11 +5182,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5233,6 +5229,376 @@
       </c>
       <c r="B5" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>工厂名称</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>联系方式</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>工厂地址</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>联系人</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>媛媛服饰</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>13826924680</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>东莞市茶山镇卢屋路146号三楼</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>李江伟</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>嘉品服饰</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>17873622720</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>虎门镇龙眼二路36号鑫丰缩水厂</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>覃生</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>保入服饰</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>18569291582</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>广东省东莞市虎门镇，镇兴路22号2楼，A幢</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>周水晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>晓松服饰</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>13686183553</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>虎门威远武山沙工业区一路二号五楼</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>李业玲</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>祺创服饰</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>13662784782</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>虎门卢联市场东门3号3楼</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>唐华</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>佳彤服饰</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>18173936246</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>东莞市虎门镇卢屋向西埗头工业区2号佳彤服饰</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>小慧</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>增裕服饰</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>13694924318</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>东莞市虎门镇龙眼社区龙眼七路 23号增裕制衣有限公司</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>吴生</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>荷帆服饰</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>18826835827</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>广东省东莞市虎门镇镇口东方三路2号顺成服饰产业园1栋101室</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>陈国祥</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>金服兴服饰</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>13712658918</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>广东省东莞市虎门镇镇口工业二路1号101室金服兴時装有限公司</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>黄树林</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>润创服饰</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>18929149227</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>虎门镇，镇口第一工业区A22栋5楼</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>余华</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>臻线服饰</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>15338353398</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>广东省东莞市虎门镇太宝路75号后座4楼</t>
+        </is>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>聚进服饰</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>13392711582</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>东莞市虎门镇龙眼工业路29一楼</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>石强</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>茗华服饰</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>18925559555</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>广东东莞虎门镇口博美步行街5号1栋2楼</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>林开</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>速优服饰</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>18025168098</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>广东省东莞市虎门镇连升北路社岗综合市场利丰楼5楼</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>王勇</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>瑞华服饰</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>18680901551</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>虎门镇镇口第一工业区镇兴路129号</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>许建华</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>梓洪服饰</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>13268525999</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>虎门镇龙眼工业路12号B栋四楼梓洪服饰有限公司</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>胡生</t>
+        </is>
       </c>
     </row>
   </sheetData>
